--- a/chybove_hlasenia.xlsx
+++ b/chybove_hlasenia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marko\Documents\VUT FIT\ifj\proj\ifj-projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{302DC035-444C-4585-9A91-C655245A440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C51D90-DA2A-4A81-A7AA-C675166AE6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{3659E002-BE5E-4071-95AA-5C6DB9B812AC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Popis</t>
   </si>
@@ -97,10 +97,6 @@
   <si>
     <t>Definice funkce se skládá z hlavičky a těla funkce. Definice funkce je zároveň její dekla-
 rací. Každá použitá funkce musí být definovaná, jinak končí analýza chybou</t>
-  </si>
-  <si>
-    <t>Přetěžování
-funkcí (angl. overloading) je v IFJ24 zakázáno</t>
   </si>
   <si>
     <t>Definice funkce nemusí lexikálně předcházet kódu pro použití této funkce, tzv. volání
@@ -379,6 +375,38 @@
 funkce obsahuje jiný počet nebo typy skutečných parametrů, než funkce očekává
 (tedy než je uvedeno v její hlavičce, a to i u vestavěných funkcí, včetně případného
 předání null, kde to není očekáváno) (rovnako platí pre vstavané funkcie)</t>
+  </si>
+  <si>
+    <t>10 (2?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">redefinice argumentu
+funkce </t>
+  </si>
+  <si>
+    <t>fn zmenHodnotu(a: i32) void {
+    const a = 40;
+}</t>
+  </si>
+  <si>
+    <t>Redefinice funkce</t>
+  </si>
+  <si>
+    <t>nevyužitý argument funkce</t>
+  </si>
+  <si>
+    <t>fn zmenHodnotu(a: i32) void {
+ const b = 4;
+}</t>
+  </si>
+  <si>
+    <t>prepisanie const</t>
+  </si>
+  <si>
+    <t>fn zmenHodnotu(a: i32) void {
+ const b = 4;
+ b = 54;
+}</t>
   </si>
 </sst>
 </file>
@@ -423,12 +451,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,11 +808,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211D308D-60D8-4BE9-B02A-C075AD8DBF70}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="26.15" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="45.23046875" customWidth="1"/>
-    <col min="2" max="2" width="22.4609375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.4609375" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.69140625" customWidth="1"/>
     <col min="4" max="4" width="77.3046875" customWidth="1"/>
     <col min="5" max="5" width="35.15234375" customWidth="1"/>
@@ -795,7 +822,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -812,8 +839,11 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>3</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -821,8 +851,11 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -835,8 +868,11 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3">
-        <v>10</v>
+      <c r="B4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -846,8 +882,11 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -857,7 +896,7 @@
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -868,262 +907,361 @@
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="111.9" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="3">
-        <v>10</v>
+        <v>65</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="192" x14ac:dyDescent="0.7">
       <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
+      <c r="C9">
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="71.150000000000006" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="3">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="31.75" x14ac:dyDescent="0.7">
       <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="3">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2">
         <v>6</v>
       </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="46.3" x14ac:dyDescent="0.7">
       <c r="A12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="3">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2">
         <v>4</v>
       </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="75.45" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" s="3">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="46.3" x14ac:dyDescent="0.7">
       <c r="A14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" s="3">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="46.3" x14ac:dyDescent="0.7">
       <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B15" s="3">
-        <v>8</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="104.6" x14ac:dyDescent="0.7">
       <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" s="3">
-        <v>7</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="133.75" x14ac:dyDescent="0.7">
       <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="90" x14ac:dyDescent="0.7">
       <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="3">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="192" x14ac:dyDescent="0.7">
       <c r="A19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="3">
+        <v>61</v>
+      </c>
+      <c r="B19" s="2">
         <v>4</v>
       </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
       <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="2">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B20" s="3">
-        <v>6</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="133.75" x14ac:dyDescent="0.7">
       <c r="A21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" s="3">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="119.15" x14ac:dyDescent="0.7">
       <c r="A22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" s="3">
-        <v>4</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="104.6" x14ac:dyDescent="0.7">
       <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="2">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B23" s="3">
-        <v>6</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="90" x14ac:dyDescent="0.7">
       <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="2">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B24" s="3">
-        <v>6</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="133.75" x14ac:dyDescent="0.7">
       <c r="A25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="3">
+        <v>51</v>
+      </c>
+      <c r="B25" s="2">
         <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="177.45" x14ac:dyDescent="0.7">
       <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="2">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B26" s="3">
-        <v>7</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="148.30000000000001" x14ac:dyDescent="0.7">
       <c r="A27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="3">
+        <v>55</v>
+      </c>
+      <c r="B27" s="2">
         <v>7</v>
       </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="31.75" x14ac:dyDescent="0.7">
       <c r="A28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="3">
+        <v>56</v>
+      </c>
+      <c r="B28" s="2">
         <v>7</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="119.15" x14ac:dyDescent="0.7">
       <c r="A29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="3">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2">
         <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
       <c r="A30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="2">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="3">
-        <v>7</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>61</v>
-      </c>
+    </row>
+    <row r="31" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
+      <c r="A31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="2">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
+      <c r="A32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
+      <c r="A33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="2">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="D34" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
@@ -1131,7 +1269,7 @@
       <formula>LEN(TRIM(C1))=0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"Dokončené"</formula>
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/chybove_hlasenia.xlsx
+++ b/chybove_hlasenia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marko\Documents\VUT FIT\ifj\proj\ifj-projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C51D90-DA2A-4A81-A7AA-C675166AE6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3ABBF0-6AD6-4647-A2C9-F4D62DD2897B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{3659E002-BE5E-4071-95AA-5C6DB9B812AC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Popis</t>
   </si>
@@ -361,14 +361,6 @@
   <si>
     <t>Žádný z operátorů nelze aplikovat na řezy
  nebo řetězcové literály.</t>
-  </si>
-  <si>
-    <t>Bez rozšíření
-BOOLTHEN není s výsledkem porovnání (pravdivostní hodnota) možné dále pracovat a
-lze jej využít pouze u podmínek příkazů if a while</t>
-  </si>
-  <si>
-    <t>TODO</t>
   </si>
   <si>
     <t>V případě, že příkaz volání
@@ -869,7 +861,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -919,7 +911,7 @@
     </row>
     <row r="8" spans="1:5" ht="111.9" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1050,6 +1042,9 @@
       <c r="B17" s="2">
         <v>7</v>
       </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
       <c r="D17" s="1" t="s">
         <v>38</v>
       </c>
@@ -1061,13 +1056,16 @@
       <c r="B18" s="2">
         <v>8</v>
       </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
       <c r="D18" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="192" x14ac:dyDescent="0.7">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -1212,27 +1210,30 @@
     </row>
     <row r="30" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
       <c r="A31" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B31" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
@@ -1242,25 +1243,15 @@
       <c r="B32" s="2">
         <v>5</v>
       </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
       <c r="D32" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="60.9" x14ac:dyDescent="0.7">
-      <c r="A33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="2">
-        <v>5</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A34" s="1"/>
       <c r="D34" s="1"/>
     </row>
   </sheetData>

--- a/chybove_hlasenia.xlsx
+++ b/chybove_hlasenia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marko\Documents\VUT FIT\ifj\proj\ifj-projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3ABBF0-6AD6-4647-A2C9-F4D62DD2897B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC048E3-5487-4280-847C-27F7CDD77969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{3659E002-BE5E-4071-95AA-5C6DB9B812AC}"/>
   </bookViews>
